--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -285,7 +285,7 @@
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
-    <t>Messbefunde.BMI</t>
+    <t>Messbefunde.bmi</t>
   </si>
   <si>
     <t>Event</t>
@@ -972,7 +972,7 @@
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
-    <t>Messbefunde.BMI.DatumBMI</t>
+    <t>Messbefunde.bmi.datumBMI</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1091,7 +1091,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>Messbefunde.BMI.BMI</t>
+    <t>Messbefunde.bmi.bmi</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -285,7 +285,7 @@
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
-    <t>Messbefunde.bmi</t>
+    <t>koerperlicheUntersuchung.bmi</t>
   </si>
   <si>
     <t>Event</t>
@@ -889,7 +889,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>Patient</t>
+    <t>persoenlicheInfosIndexpatient</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -972,7 +972,7 @@
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
-    <t>Messbefunde.bmi.datumBMI</t>
+    <t>koerperlicheUntersuchung.bmi.datumBMI</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1091,7 +1091,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>Messbefunde.bmi.bmi</t>
+    <t>koerperlicheUntersuchung.bmi.bmi</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-bodymassindex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
